--- a/hddt/templates/misa_mua_hang_khong_qua_kho_vnd.xlsx
+++ b/hddt/templates/misa_mua_hang_khong_qua_kho_vnd.xlsx
@@ -507,6 +507,7 @@
     <col width="15.99" customWidth="1" style="28" min="1" max="1"/>
     <col width="21.99" customWidth="1" style="29" min="2" max="2"/>
     <col width="23.56" customWidth="1" style="29" min="3" max="4"/>
+    <col width="23.5703125" customWidth="1" style="46" min="4" max="4"/>
     <col width="18.85" customWidth="1" style="30" min="5" max="5"/>
     <col width="18.56" customWidth="1" style="30" min="6" max="6"/>
     <col width="21.42" customWidth="1" style="31" min="7" max="7"/>
